--- a/Excel Class Files/Excel Projects/HR Analytics.xlsx
+++ b/Excel Class Files/Excel Projects/HR Analytics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\Excel Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{643870B7-00A2-4AFA-9D8A-8DA3B5CB59D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5C6BC4-4727-4BB8-8D0D-DB691BF7A41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F2AC0E08-5FC8-4FD8-BCA5-807334643334}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11821" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11822" uniqueCount="88">
   <si>
     <t>Age</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>Group DistanceFromHome into useful ranges if needed, then compare counts by distance range and Attrition.</t>
+  </si>
+  <si>
+    <t>Sno</t>
   </si>
 </sst>
 </file>
@@ -741,16 +744,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,7 +802,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -812,13 +815,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1176,179 +1188,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C378A7E-380E-474A-B343-027F4919EFCB}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.9140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="45.5" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="1" width="8.6640625" style="3"/>
+    <col min="2" max="2" width="31.9140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="45.5" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:3" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:3" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="11" t="s">
         <v>86</v>
       </c>
     </row>
